--- a/rooster.xlsx
+++ b/rooster.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d6ee1c3f8a387310/Bureaublad/RoosterApp/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="131" documentId="11_399CEF4266DF04CE7CBBBB2563658F94438DDF75" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1342FEF3-EC9A-4B0C-BD89-1715E876681D}"/>
+  <xr:revisionPtr revIDLastSave="132" documentId="11_399CEF4266DF04CE7CBBBB2563658F94438DDF75" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D549CABD-AB5D-4362-B7B1-5BCC0ABBDFC1}"/>
   <bookViews>
-    <workbookView xWindow="5835" yWindow="1020" windowWidth="18000" windowHeight="9270" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="5835" yWindow="1020" windowWidth="18000" windowHeight="9270" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Rooster" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="34">
   <si>
     <t>Dag</t>
   </si>
@@ -121,9 +121,6 @@
   </si>
   <si>
     <t>Positie</t>
-  </si>
-  <si>
-    <t>Pucy</t>
   </si>
   <si>
     <t>Dienst</t>
@@ -770,7 +767,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -824,7 +821,7 @@
         <v>31</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -885,7 +882,7 @@
         <v>8</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">

--- a/rooster.xlsx
+++ b/rooster.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d6ee1c3f8a387310/Bureaublad/RoosterApp/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="132" documentId="11_399CEF4266DF04CE7CBBBB2563658F94438DDF75" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D549CABD-AB5D-4362-B7B1-5BCC0ABBDFC1}"/>
+  <xr:revisionPtr revIDLastSave="143" documentId="11_399CEF4266DF04CE7CBBBB2563658F94438DDF75" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{21705AC5-F377-486B-BF35-E2E09DEE2D16}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="5835" yWindow="1020" windowWidth="18000" windowHeight="9270" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5835" yWindow="1020" windowWidth="18000" windowHeight="9270" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Rooster" sheetId="1" r:id="rId1"/>
@@ -871,7 +871,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36B99BDE-3C32-4796-A355-210776F429BE}">
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="13.28515625" customWidth="1"/>
@@ -922,6 +922,46 @@
         <v>47</v>
       </c>
       <c r="B6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>48</v>
+      </c>
+      <c r="B7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>49</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>50</v>
+      </c>
+      <c r="B9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>51</v>
+      </c>
+      <c r="B10">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>52</v>
+      </c>
+      <c r="B11">
         <v>4</v>
       </c>
     </row>

--- a/rooster.xlsx
+++ b/rooster.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d6ee1c3f8a387310/Bureaublad/RoosterApp/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="143" documentId="11_399CEF4266DF04CE7CBBBB2563658F94438DDF75" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{21705AC5-F377-486B-BF35-E2E09DEE2D16}"/>
+  <xr:revisionPtr revIDLastSave="147" documentId="11_399CEF4266DF04CE7CBBBB2563658F94438DDF75" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C9F63E33-F517-4C38-AD7E-C95797DEC7EA}"/>
   <bookViews>
-    <workbookView xWindow="5835" yWindow="1020" windowWidth="18000" windowHeight="9270" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="5835" yWindow="1020" windowWidth="18000" windowHeight="9270" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Rooster" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="32">
   <si>
     <t>Dag</t>
   </si>
@@ -33,21 +33,12 @@
     <t>Gebruiker</t>
   </si>
   <si>
-    <t>Bijzonderheden</t>
-  </si>
-  <si>
     <t>Datum</t>
   </si>
   <si>
     <t>Maandag</t>
   </si>
   <si>
-    <t>onbekend</t>
-  </si>
-  <si>
-    <t>kan</t>
-  </si>
-  <si>
     <t>Naam</t>
   </si>
   <si>
@@ -127,6 +118,9 @@
   </si>
   <si>
     <t>Verschuiving</t>
+  </si>
+  <si>
+    <t>Meldingen</t>
   </si>
 </sst>
 </file>
@@ -587,158 +581,158 @@
   <sheetData>
     <row r="1" spans="1:8" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="H1" s="5" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B2" s="2">
         <v>43</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B3" s="2">
         <v>43</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B4" s="2">
         <v>43</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B5" s="2">
         <v>43</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B6" s="2">
         <v>43</v>
       </c>
       <c r="C6" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H6" s="6" t="s">
         <v>27</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="H6" s="6" t="s">
-        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -756,10 +750,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -767,7 +761,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -775,7 +769,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -783,7 +777,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -791,7 +785,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -799,7 +793,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -818,10 +812,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -829,7 +823,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -837,7 +831,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -845,7 +839,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -853,7 +847,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -861,7 +855,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -879,10 +873,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -981,50 +975,50 @@
   <sheetData>
     <row r="1" spans="1:2" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -1034,7 +1028,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="10.42578125" customWidth="1"/>
@@ -1049,25 +1043,14 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1" t="s">
         <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4"/>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" t="s">
-        <v>6</v>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
